--- a/project_final_testcase/Member_2_Final_STQA_Test_Cases.xlsx
+++ b/project_final_testcase/Member_2_Final_STQA_Test_Cases.xlsx
@@ -3,7 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Member 2 Final STQA" sheetId="1" r:id="rId1"/>
+    <sheet name="Overview" sheetId="1" r:id="rId1"/>
+    <sheet name="Test_Cases" sheetId="2" r:id="rId2"/>
+    <sheet name="BVA" sheetId="3" r:id="rId3"/>
+    <sheet name="ECT_DecisionTable" sheetId="4" r:id="rId4"/>
+    <sheet name="Basis_Path" sheetId="5" r:id="rId5"/>
+    <sheet name="Bug_Reports" sheetId="6" r:id="rId6"/>
+    <sheet name="Automation_Coverage" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -397,1516 +403,3456 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:D23"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="32.83203125" customWidth="1"/>
-    <col min="6" max="6" width="36.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
-    <col min="8" max="8" width="55.83203125" customWidth="1"/>
-    <col min="9" max="9" width="45.83203125" customWidth="1"/>
-    <col min="10" max="10" width="45.83203125" customWidth="1"/>
-    <col min="11" max="11" width="50.83203125" customWidth="1"/>
-    <col min="12" max="12" width="55.83203125" customWidth="1"/>
-    <col min="13" max="13" width="55.83203125" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
-    <col min="15" max="15" width="70.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="45.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="55.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Testing Technique</v>
+        <v>Shopfinity — STQA Test Workbook (Member 2)</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Team and modules</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Member</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Module</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Test cases</v>
+      </c>
+      <c r="D4" t="str">
+        <v>BVA module</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Shopping Cart &amp; Inventory Control</v>
+      </c>
+      <c r="C5">
+        <v>30</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Add to cart — item quantity (min 1, max 99)</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Where each required STQA concept is demonstrated</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>#</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Concept</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Evidence</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Tab / file</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Boundary Value Analysis (1 module per member)</v>
+      </c>
+      <c r="C9" t="str">
+        <v>5 modules, 32 boundary cases (6-position analysis: min-1, min, min+1, max-1, max, max+1)</v>
+      </c>
+      <c r="D9" t="str">
+        <v>BVA tab; M1_TC_001–005, M2_TC_001–005, M3_TC_001–008, M4_TC_001–008, M5_TC_001–006</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Equivalence Class Testing / Decision Table</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Equivalence classes across 12 input domains; 4 formal decision tables</v>
+      </c>
+      <c r="D10" t="str">
+        <v>ECT_DecisionTable tab; M1_TC_020–023, M2_TC_018–022, M3_TC_009–014, M4_TC_009–016, M5_TC_019–030</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Basis Path Testing (5 modules per member)</v>
+      </c>
+      <c r="C11" t="str">
+        <v>25 routine allocations across 5 members (22 unique routines, 5 distinct per member, V(G)=3 to 6)</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Basis_Path tab; M1_TC_006–019, M2_TC_006–017, M3_TC_015–030, M4_TC_017–030, M5_TC_007–018</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Test Case Design and Execution (30 each)</v>
+      </c>
+      <c r="C12" t="str">
+        <v>30 cases with preconditions, steps, test data, expected/actual result, status, priority</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Test_Cases tab</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>5</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Bug / Defect Reporting (around 30)</v>
+      </c>
+      <c r="C13" t="str">
+        <v>30 verified defects (13 application defects, 11 automation setup issues, 6 rate-limit/infra blockers)</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Bug_Reports tab</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>6</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Unit testing (JUnit / Jest equivalent)</v>
+      </c>
+      <c r="C14" t="str">
+        <v>64 offline unit regression tests (pure logic, schemas, error handler, rate limiter, state machine, service mocks)</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Automation_Coverage tab; tests/phase2a-regression.ts</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Automation testing (Selenium / Playwright equivalent)</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Playwright E2E and API test suites stored under tests/ root directory</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Automation_Coverage tab; tests/member[1-5]/test_cases/</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>• Exactly 150 test cases total across 5 members (30 per member) derived from actual Shopfinity source code.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>• Status "Pass" is the result of executed tests (101 verified passes). Cases not executed in the current cycle retain "Not Run" (49 cases) to protect live database integrity.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>• Automated_By column provides the exact test script path and TC identifier.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>• Defect_Ref cross-references the Bug_Reports sheet for test cases associated with observed defects.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>• Basis Path testing evaluates 5 distinct procedural routines per member with cyclomatic complexity V(G) and independent basis paths.</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>• In-memory service mocks (categoryService.update, cartService.mergeCart) are explicitly disclosed as supplementary unit mock evidence.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D23"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N31"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="45.83203125" customWidth="1"/>
+    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+    <col min="7" max="7" width="55.83203125" customWidth="1"/>
+    <col min="8" max="8" width="35.83203125" customWidth="1"/>
+    <col min="9" max="9" width="55.83203125" customWidth="1"/>
+    <col min="10" max="10" width="55.83203125" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" customWidth="1"/>
+    <col min="13" max="13" width="45.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>TC_ID</v>
       </c>
       <c r="B1" t="str">
         <v>Member</v>
       </c>
       <c r="C1" t="str">
-        <v>Test ID</v>
+        <v>Module</v>
       </c>
       <c r="D1" t="str">
-        <v>Module</v>
+        <v>Technique</v>
       </c>
       <c r="E1" t="str">
-        <v>Function / Component</v>
+        <v>Title</v>
       </c>
       <c r="F1" t="str">
-        <v>File Path</v>
+        <v>Preconditions</v>
       </c>
       <c r="G1" t="str">
-        <v>Test Case Description</v>
+        <v>Steps</v>
       </c>
       <c r="H1" t="str">
-        <v>Scenario</v>
+        <v>Test_Data</v>
       </c>
       <c r="I1" t="str">
-        <v>Test Data</v>
+        <v>Expected_Result</v>
       </c>
       <c r="J1" t="str">
-        <v>Pre-Condition</v>
+        <v>Actual_Result</v>
       </c>
       <c r="K1" t="str">
-        <v>Steps for Execution</v>
+        <v>Status</v>
       </c>
       <c r="L1" t="str">
-        <v>Expected Result</v>
+        <v>Priority</v>
       </c>
       <c r="M1" t="str">
-        <v>Actual Result</v>
+        <v>Automated_By</v>
       </c>
       <c r="N1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Comment</v>
+        <v>Defect_Ref</v>
       </c>
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>Boundary Value Analysis (BVA)</v>
+        <v>M2_TC_001</v>
       </c>
       <c r="B2" t="str">
         <v>Member 2</v>
       </c>
       <c r="C2" t="str">
-        <v>M2_TC_001</v>
+        <v>Cart &amp; Inventory</v>
       </c>
       <c r="D2" t="str">
-        <v>Cart &amp; Inventory</v>
+        <v>BVA</v>
       </c>
       <c r="E2" t="str">
-        <v>addCartItemSchema</v>
+        <v>BVA: Add to cart quantity Min-1 (quantity=0)</v>
       </c>
       <c r="F2" t="str">
-        <v>lib/validations/cart.ts</v>
-      </c>
-      <c r="G2" t="str">
-        <v>BVA: Add to cart quantity Min-1 (quantity=0)</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Validating add-to-cart item quantity lower boundary</v>
-      </c>
-      <c r="I2" t="str">
-        <v>quantity=0</v>
-      </c>
-      <c r="J2" t="str">
         <v>Customer is authenticated</v>
       </c>
-      <c r="K2" t="str" xml:space="preserve">
+      <c r="G2" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Submit POST /api/cart/items with { productId, quantity: 0 }
 2. Inspect response error</v>
       </c>
+      <c r="H2" t="str">
+        <v>quantity=0</v>
+      </c>
+      <c r="I2" t="str">
+        <v>HTTP 400 Bad Request with validation error: quantity must be &gt;= 1</v>
+      </c>
+      <c r="J2" t="str">
+        <v>HTTP 400 Bad Request returned</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L2" t="str">
-        <v>HTTP 400 Bad Request with validation error: quantity must be &gt;= 1</v>
+        <v>High</v>
       </c>
       <c r="M2" t="str">
-        <v>HTTP 400 Bad Request returned</v>
+        <v>Unit · tests/phase2a-regression.ts · addCartItemSchema &amp; Stock Bounds (M2_TC_001)</v>
       </c>
       <c r="N2" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O2" t="str">
-        <v>Verified via automated offline regression test suite (tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>DEF-12</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>Boundary Value Analysis (BVA)</v>
+        <v>M2_TC_002</v>
       </c>
       <c r="B3" t="str">
         <v>Member 2</v>
       </c>
       <c r="C3" t="str">
-        <v>M2_TC_002</v>
+        <v>Cart &amp; Inventory</v>
       </c>
       <c r="D3" t="str">
-        <v>Cart &amp; Inventory</v>
+        <v>BVA</v>
       </c>
       <c r="E3" t="str">
-        <v>addCartItemSchema</v>
+        <v>BVA: Add to cart quantity Min (quantity=1)</v>
       </c>
       <c r="F3" t="str">
-        <v>lib/validations/cart.ts</v>
-      </c>
-      <c r="G3" t="str">
-        <v>BVA: Add to cart quantity Min (quantity=1)</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Validating add-to-cart item quantity minimum allowed value</v>
-      </c>
-      <c r="I3" t="str">
-        <v>quantity=1</v>
-      </c>
-      <c r="J3" t="str">
         <v>Product in stock with stockQuantity &gt;= 1</v>
       </c>
-      <c r="K3" t="str" xml:space="preserve">
+      <c r="G3" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Submit POST /api/cart/items with { productId, quantity: 1 }
 2. Inspect response</v>
       </c>
+      <c r="H3" t="str">
+        <v>quantity=1</v>
+      </c>
+      <c r="I3" t="str">
+        <v>HTTP 201 Created with cart item quantity=1</v>
+      </c>
+      <c r="J3" t="str">
+        <v>HTTP 201 Created returned with cart item</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L3" t="str">
-        <v>HTTP 201 Created with cart item quantity=1</v>
+        <v>High</v>
       </c>
       <c r="M3" t="str">
-        <v>HTTP 201 Created returned with cart item</v>
+        <v>Unit · tests/phase2a-regression.ts · addCartItemSchema &amp; Stock Bounds (M2_TC_002)</v>
       </c>
       <c r="N3" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Verified via automated offline regression test suite (tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>Boundary Value Analysis (BVA)</v>
+        <v>M2_TC_003</v>
       </c>
       <c r="B4" t="str">
         <v>Member 2</v>
       </c>
       <c r="C4" t="str">
-        <v>M2_TC_003</v>
+        <v>Cart &amp; Inventory</v>
       </c>
       <c r="D4" t="str">
-        <v>Cart &amp; Inventory</v>
+        <v>BVA</v>
       </c>
       <c r="E4" t="str">
-        <v>addCartItemSchema</v>
+        <v>BVA: Add to cart quantity Nominal (quantity=50)</v>
       </c>
       <c r="F4" t="str">
-        <v>lib/validations/cart.ts</v>
-      </c>
-      <c r="G4" t="str">
-        <v>BVA: Add to cart quantity Nominal (quantity=50)</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Validating add-to-cart item quantity at standard midpoint</v>
-      </c>
-      <c r="I4" t="str">
-        <v>quantity=50</v>
-      </c>
-      <c r="J4" t="str">
         <v>Product has stockQuantity &gt;= 50</v>
       </c>
-      <c r="K4" t="str" xml:space="preserve">
+      <c r="G4" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Submit POST /api/cart/items with { productId, quantity: 50 }
 2. Verify cart response</v>
       </c>
+      <c r="H4" t="str">
+        <v>quantity=50</v>
+      </c>
+      <c r="I4" t="str">
+        <v>HTTP 201 Created with quantity=50</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Not Run</v>
+      </c>
       <c r="L4" t="str">
-        <v>HTTP 201 Created with quantity=50</v>
+        <v>High</v>
       </c>
       <c r="M4" t="str">
-        <v>Not Run</v>
+        <v>Planned Playwright · tests/member2/ · M2_TC_003 (Offline - requires non-prod DB / staging rate limit)</v>
       </c>
       <c r="N4" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O4" t="str">
-        <v>Unexecuted against live environment in compliance with project safety constraints (no production DB mutations / synthetic orders). Retained as validated specification.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="5" xml:space="preserve">
       <c r="A5" t="str">
-        <v>Boundary Value Analysis (BVA)</v>
+        <v>M2_TC_004</v>
       </c>
       <c r="B5" t="str">
         <v>Member 2</v>
       </c>
       <c r="C5" t="str">
-        <v>M2_TC_004</v>
+        <v>Cart &amp; Inventory</v>
       </c>
       <c r="D5" t="str">
-        <v>Cart &amp; Inventory</v>
+        <v>BVA</v>
       </c>
       <c r="E5" t="str">
-        <v>addCartItemSchema</v>
+        <v>BVA: Add to cart quantity Max (quantity=99)</v>
       </c>
       <c r="F5" t="str">
-        <v>lib/validations/cart.ts</v>
-      </c>
-      <c r="G5" t="str">
-        <v>BVA: Add to cart quantity Max (quantity=99)</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Validating add-to-cart item quantity at maximum allowed limit</v>
-      </c>
-      <c r="I5" t="str">
-        <v>quantity=99</v>
-      </c>
-      <c r="J5" t="str">
         <v>Product has stockQuantity &gt;= 99</v>
       </c>
-      <c r="K5" t="str" xml:space="preserve">
+      <c r="G5" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Submit POST /api/cart/items with { productId, quantity: 99 }
 2. Verify cart response</v>
       </c>
+      <c r="H5" t="str">
+        <v>quantity=99</v>
+      </c>
+      <c r="I5" t="str">
+        <v>HTTP 201 Created with quantity=99</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Item added with quantity 99</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L5" t="str">
-        <v>HTTP 201 Created with quantity=99</v>
+        <v>High</v>
       </c>
       <c r="M5" t="str">
-        <v>Item added with quantity 99</v>
+        <v>Unit · tests/phase2a-regression.ts · addCartItemSchema &amp; Stock Bounds (M2_TC_004)</v>
       </c>
       <c r="N5" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O5" t="str">
-        <v>Verified via automated offline regression test suite (tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
       <c r="A6" t="str">
-        <v>Boundary Value Analysis (BVA)</v>
+        <v>M2_TC_005</v>
       </c>
       <c r="B6" t="str">
         <v>Member 2</v>
       </c>
       <c r="C6" t="str">
-        <v>M2_TC_005</v>
+        <v>Cart &amp; Inventory</v>
       </c>
       <c r="D6" t="str">
-        <v>Cart &amp; Inventory</v>
+        <v>BVA</v>
       </c>
       <c r="E6" t="str">
-        <v>addCartItemSchema</v>
+        <v>BVA: Add to cart quantity Max+1 (quantity=100)</v>
       </c>
       <c r="F6" t="str">
-        <v>lib/validations/cart.ts</v>
-      </c>
-      <c r="G6" t="str">
-        <v>BVA: Add to cart quantity Max+1 (quantity=100)</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Validating add-to-cart item quantity above maximum allowed limit</v>
-      </c>
-      <c r="I6" t="str">
-        <v>quantity=100</v>
-      </c>
-      <c r="J6" t="str">
         <v>Product has stockQuantity &gt;= 100</v>
       </c>
-      <c r="K6" t="str" xml:space="preserve">
+      <c r="G6" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Submit POST /api/cart/items with { productId, quantity: 100 }
 2. Verify cart response</v>
       </c>
+      <c r="H6" t="str">
+        <v>quantity=100</v>
+      </c>
+      <c r="I6" t="str">
+        <v>HTTP 400 Bad Request with validation error: Maximum 99</v>
+      </c>
+      <c r="J6" t="str">
+        <v>HTTP 400 Bad Request returned rejecting quantity 100</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L6" t="str">
-        <v>HTTP 400 Bad Request with validation error: Maximum 99</v>
+        <v>High</v>
       </c>
       <c r="M6" t="str">
-        <v>HTTP 400 Bad Request returned rejecting quantity 100</v>
+        <v>Unit · tests/phase2a-regression.ts · addCartItemSchema &amp; Stock Bounds (M2_TC_005)</v>
       </c>
       <c r="N6" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O6" t="str">
-        <v>Verified via automated offline regression test suite (tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>DEF-13</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
       <c r="A7" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M2_TC_006</v>
       </c>
       <c r="B7" t="str">
         <v>Member 2</v>
       </c>
       <c r="C7" t="str">
-        <v>M2_TC_006</v>
+        <v>Cart &amp; Inventory</v>
       </c>
       <c r="D7" t="str">
-        <v>Cart &amp; Inventory</v>
+        <v>Basis Path</v>
       </c>
       <c r="E7" t="str">
-        <v>cartService.updateQuantity</v>
+        <v>BP: updateQuantity Path 1 - Cart item not found throws NotFoundError</v>
       </c>
       <c r="F7" t="str">
-        <v>lib/services/cart-service.ts</v>
-      </c>
-      <c r="G7" t="str">
-        <v>BP: updateQuantity Path 1 - Cart item not found throws NotFoundError</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Attempting to update quantity of non-existent cart item</v>
-      </c>
-      <c r="I7" t="str">
-        <v>itemId = "non-existent-item-uuid"</v>
-      </c>
-      <c r="J7" t="str">
         <v>User has active cart without item "non-existent-item-uuid"</v>
       </c>
-      <c r="K7" t="str" xml:space="preserve">
+      <c r="G7" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute cartService.updateQuantity(userId, "non-existent-item-uuid", { quantity: 2 })
 2. Catch exception</v>
       </c>
+      <c r="H7" t="str">
+        <v>itemId = "non-existent-item-uuid"</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Throws NotFoundError("CartItem", "non-existent-item-uuid")</v>
+      </c>
+      <c r="J7" t="str">
+        <v>NotFoundError thrown as expected</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L7" t="str">
-        <v>Throws NotFoundError("CartItem", "non-existent-item-uuid")</v>
+        <v>Medium</v>
       </c>
       <c r="M7" t="str">
-        <v>NotFoundError thrown as expected</v>
+        <v>Unit · tests/phase2a-regression.ts · DEF-04/DEF-09 Stock Overflow &amp; Zero Qty (M2_TC_006)</v>
       </c>
       <c r="N7" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O7" t="str">
-        <v>Verified via automated offline regression test suite (tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
       <c r="A8" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M2_TC_007</v>
       </c>
       <c r="B8" t="str">
         <v>Member 2</v>
       </c>
       <c r="C8" t="str">
-        <v>M2_TC_007</v>
+        <v>Cart &amp; Inventory</v>
       </c>
       <c r="D8" t="str">
-        <v>Cart &amp; Inventory</v>
+        <v>Basis Path</v>
       </c>
       <c r="E8" t="str">
-        <v>cartService.updateQuantity</v>
+        <v>BP: updateQuantity Path 2 - Quantity &lt;= 0 deletes item from cart</v>
       </c>
       <c r="F8" t="str">
-        <v>lib/services/cart-service.ts</v>
-      </c>
-      <c r="G8" t="str">
-        <v>BP: updateQuantity Path 2 - Quantity &lt;= 0 deletes item from cart</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Customer decrements cart item quantity to zero or negative</v>
-      </c>
-      <c r="I8" t="str">
-        <v>itemId = existingItemId, quantity = 0</v>
-      </c>
-      <c r="J8" t="str">
         <v>Cart contains existing item</v>
       </c>
-      <c r="K8" t="str" xml:space="preserve">
+      <c r="G8" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute cartService.updateQuantity(userId, existingItemId, { quantity: 0 })
 2. Query cart in DB</v>
       </c>
+      <c r="H8" t="str">
+        <v>itemId = existingItemId, quantity = 0</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Item deleted from CartItem table; updated cart returned without the item</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Item deleted and cart itemsCount decreased</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L8" t="str">
-        <v>Item deleted from CartItem table; updated cart returned without the item</v>
+        <v>Medium</v>
       </c>
       <c r="M8" t="str">
-        <v>Item deleted and cart itemsCount decreased</v>
+        <v>Unit · tests/phase2a-regression.ts · DEF-04/DEF-09 Stock Overflow &amp; Zero Qty (M2_TC_007)</v>
       </c>
       <c r="N8" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O8" t="str">
-        <v>Verified via automated offline regression test suite (tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
       <c r="A9" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M2_TC_008</v>
       </c>
       <c r="B9" t="str">
         <v>Member 2</v>
       </c>
       <c r="C9" t="str">
-        <v>M2_TC_008</v>
+        <v>Cart &amp; Inventory</v>
       </c>
       <c r="D9" t="str">
-        <v>Cart &amp; Inventory</v>
+        <v>Basis Path</v>
       </c>
       <c r="E9" t="str">
-        <v>cartService.updateQuantity</v>
+        <v>BP: updateQuantity Path 3 - Product unavailable throws NotFoundError</v>
       </c>
       <c r="F9" t="str">
-        <v>lib/services/cart-service.ts</v>
-      </c>
-      <c r="G9" t="str">
-        <v>BP: updateQuantity Path 3 - Product unavailable throws NotFoundError</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Cart item product was unpublished or soft-deleted before update</v>
-      </c>
-      <c r="I9" t="str">
-        <v>itemId with product where isPublished=false</v>
-      </c>
-      <c r="J9" t="str">
         <v>Product was unpublished while remaining in user cart</v>
       </c>
-      <c r="K9" t="str" xml:space="preserve">
+      <c r="G9" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute cartService.updateQuantity(userId, itemId, { quantity: 2 })
 2. Catch exception</v>
       </c>
+      <c r="H9" t="str">
+        <v>itemId with product where isPublished=false</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Throws NotFoundError("Product", productId)</v>
+      </c>
+      <c r="J9" t="str">
+        <v>NotFoundError thrown, preventing cart update of unavailable item</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L9" t="str">
-        <v>Throws NotFoundError("Product", productId)</v>
+        <v>Medium</v>
       </c>
       <c r="M9" t="str">
-        <v>NotFoundError thrown, preventing cart update of unavailable item</v>
+        <v>Unit · tests/phase2a-regression.ts · DEF-04/DEF-09 Stock Overflow &amp; Zero Qty (M2_TC_008)</v>
       </c>
       <c r="N9" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O9" t="str">
-        <v>Verified via automated offline regression test suite (tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
       <c r="A10" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M2_TC_009</v>
       </c>
       <c r="B10" t="str">
         <v>Member 2</v>
       </c>
       <c r="C10" t="str">
-        <v>M2_TC_009</v>
+        <v>Cart &amp; Inventory</v>
       </c>
       <c r="D10" t="str">
-        <v>Cart &amp; Inventory</v>
+        <v>Basis Path</v>
       </c>
       <c r="E10" t="str">
-        <v>cartService.updateQuantity</v>
+        <v>BP: updateQuantity Path 4 - Quantity exceeds stockQuantity throws ConflictError</v>
       </c>
       <c r="F10" t="str">
-        <v>lib/services/cart-service.ts</v>
-      </c>
-      <c r="G10" t="str">
-        <v>BP: updateQuantity Path 4 - Quantity exceeds stockQuantity throws ConflictError</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Customer requests quantity higher than current stock</v>
-      </c>
-      <c r="I10" t="str">
-        <v>stockQuantity = 5, requested quantity = 8</v>
-      </c>
-      <c r="J10" t="str">
         <v>Product has only 5 units in stock</v>
       </c>
-      <c r="K10" t="str" xml:space="preserve">
+      <c r="G10" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute cartService.updateQuantity(userId, itemId, { quantity: 8 })
 2. Catch exception</v>
       </c>
+      <c r="H10" t="str">
+        <v>stockQuantity = 5, requested quantity = 8</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Throws ConflictError("Insufficient stock for ... Available: 5, requested: 8")</v>
+      </c>
+      <c r="J10" t="str">
+        <v>ConflictError thrown, preserving stock boundary</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L10" t="str">
-        <v>Throws ConflictError("Insufficient stock for ... Available: 5, requested: 8")</v>
+        <v>Medium</v>
       </c>
       <c r="M10" t="str">
-        <v>ConflictError thrown, preserving stock boundary</v>
+        <v>Unit · tests/phase2a-regression.ts · DEF-04/DEF-09 Stock Overflow &amp; Zero Qty (M2_TC_009)</v>
       </c>
       <c r="N10" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O10" t="str">
-        <v>Verified via automated offline regression test suite (tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>DEF-07</v>
       </c>
     </row>
     <row r="11" xml:space="preserve">
       <c r="A11" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M2_TC_010</v>
       </c>
       <c r="B11" t="str">
         <v>Member 2</v>
       </c>
       <c r="C11" t="str">
-        <v>M2_TC_010</v>
+        <v>Cart &amp; Inventory</v>
       </c>
       <c r="D11" t="str">
-        <v>Cart &amp; Inventory</v>
+        <v>Basis Path</v>
       </c>
       <c r="E11" t="str">
-        <v>cartService.updateQuantity</v>
+        <v>BP: updateQuantity Path 5 - Valid quantity within stock updates successfully</v>
       </c>
       <c r="F11" t="str">
-        <v>lib/services/cart-service.ts</v>
-      </c>
-      <c r="G11" t="str">
-        <v>BP: updateQuantity Path 5 - Valid quantity within stock updates successfully</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Customer updates quantity to a valid number within available inventory</v>
-      </c>
-      <c r="I11" t="str">
-        <v>stockQuantity = 10, requested quantity = 4</v>
-      </c>
-      <c r="J11" t="str">
         <v>Product has 10 units in stock</v>
       </c>
-      <c r="K11" t="str" xml:space="preserve">
+      <c r="G11" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute cartService.updateQuantity(userId, itemId, { quantity: 4 })
 2. Check updated cart</v>
       </c>
+      <c r="H11" t="str">
+        <v>stockQuantity = 10, requested quantity = 4</v>
+      </c>
+      <c r="I11" t="str">
+        <v>CartItem quantity updated to 4; updated subtotal computed and returned</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Item updated to quantity 4 and subtotal recalculated</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L11" t="str">
-        <v>CartItem quantity updated to 4; updated subtotal computed and returned</v>
+        <v>Medium</v>
       </c>
       <c r="M11" t="str">
-        <v>Item updated to quantity 4 and subtotal recalculated</v>
+        <v>Unit · tests/phase2a-regression.ts · DEF-04/DEF-09 Stock Overflow &amp; Zero Qty (M2_TC_010)</v>
       </c>
       <c r="N11" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O11" t="str">
-        <v>Verified via automated offline regression test suite (tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>DEF-08</v>
       </c>
     </row>
     <row r="12" xml:space="preserve">
       <c r="A12" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M2_TC_011</v>
       </c>
       <c r="B12" t="str">
         <v>Member 2</v>
       </c>
       <c r="C12" t="str">
-        <v>M2_TC_011</v>
+        <v>Cart &amp; Inventory</v>
       </c>
       <c r="D12" t="str">
-        <v>Cart &amp; Inventory</v>
+        <v>Basis Path</v>
       </c>
       <c r="E12" t="str">
-        <v>cartService.addItem</v>
+        <v>BP: addItem Cumulative Path - Existing item + added quantity exceeds stock</v>
       </c>
       <c r="F12" t="str">
-        <v>lib/services/cart-service.ts</v>
-      </c>
-      <c r="G12" t="str">
-        <v>BP: addItem Cumulative Path - Existing item + added quantity exceeds stock</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Customer already has 4 units in cart and attempts to add 2 more when stock is 5</v>
-      </c>
-      <c r="I12" t="str">
-        <v>stockQuantity = 5, existingQuantity = 4, incomingQuantity = 2</v>
-      </c>
-      <c r="J12" t="str">
         <v>Cart contains item with quantity 4; product stock is 5</v>
       </c>
-      <c r="K12" t="str" xml:space="preserve">
+      <c r="G12" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call cartService.addItem(userId, { productId, quantity: 2 })
 2. Catch exception</v>
       </c>
+      <c r="H12" t="str">
+        <v>stockQuantity = 5, existingQuantity = 4, incomingQuantity = 2</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Throws ConflictError("Insufficient stock ... Available: 5, total requested: 6")</v>
+      </c>
+      <c r="J12" t="str">
+        <v>ConflictError thrown, cumulative oversell prevented</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L12" t="str">
-        <v>Throws ConflictError("Insufficient stock ... Available: 5, total requested: 6")</v>
+        <v>Medium</v>
       </c>
       <c r="M12" t="str">
-        <v>ConflictError thrown, cumulative oversell prevented</v>
+        <v>Unit · tests/phase2a-regression.ts · Cumulative Cart Addition (M2_TC_011)</v>
       </c>
       <c r="N12" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O12" t="str">
-        <v>Verified via automated offline regression test suite (tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="13" xml:space="preserve">
       <c r="A13" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M2_TC_012</v>
       </c>
       <c r="B13" t="str">
         <v>Member 2</v>
       </c>
       <c r="C13" t="str">
-        <v>M2_TC_012</v>
+        <v>Cart Merging</v>
       </c>
       <c r="D13" t="str">
-        <v>Cart Merging</v>
+        <v>Basis Path</v>
       </c>
       <c r="E13" t="str">
-        <v>cartService.mergeCart</v>
+        <v>BP: mergeCart Path 1 - Empty incoming items list returns current cart</v>
       </c>
       <c r="F13" t="str">
-        <v>lib/services/cart-service.ts</v>
-      </c>
-      <c r="G13" t="str">
-        <v>BP: mergeCart Path 1 - Empty incoming items list returns current cart</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Merging guest cart when guest cart had 0 items</v>
-      </c>
-      <c r="I13" t="str">
-        <v>input.items = []</v>
-      </c>
-      <c r="J13" t="str">
         <v>Customer has existing cart with 2 items</v>
       </c>
-      <c r="K13" t="str" xml:space="preserve">
+      <c r="G13" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute cartService.mergeCart(userId, { items: [] })
 2. Check cart response</v>
       </c>
+      <c r="H13" t="str">
+        <v>input.items = []</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Returns current user cart unmodified</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Empty guest items array processed cleanly, existing user cart preserved</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L13" t="str">
-        <v>Returns current user cart unmodified</v>
+        <v>Medium</v>
       </c>
       <c r="M13" t="str">
-        <v>Empty guest items array processed cleanly, existing user cart preserved</v>
+        <v>Unit Mock · tests/phase2a-regression.ts · cartService.mergeCart &amp; Playwright (M2_TC_012)</v>
       </c>
       <c r="N13" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O13" t="str">
-        <v>Verified via Playwright E2E suite against Vercel deployment (member2/test_results/vercel-report.json); executed as mergeCart Path 1 (empty input, HTTP 200) under test title "M2_TC_011" in m2-bp-merge-cart.spec.ts.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
       <c r="A14" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M2_TC_013</v>
       </c>
       <c r="B14" t="str">
         <v>Member 2</v>
       </c>
       <c r="C14" t="str">
-        <v>M2_TC_013</v>
+        <v>Cart Merging</v>
       </c>
       <c r="D14" t="str">
-        <v>Cart Merging</v>
+        <v>Basis Path</v>
       </c>
       <c r="E14" t="str">
-        <v>cartService.mergeCart</v>
+        <v>BP: mergeCart Path 2 - Unavailable incoming products skipped with warning</v>
       </c>
       <c r="F14" t="str">
-        <v>lib/services/cart-service.ts</v>
-      </c>
-      <c r="G14" t="str">
-        <v>BP: mergeCart Path 2 - Unavailable incoming products skipped with warning</v>
-      </c>
-      <c r="H14" t="str">
-        <v>Guest cart contains product that became soft-deleted or unpublished</v>
-      </c>
-      <c r="I14" t="str">
-        <v>incoming items contains deleted productId</v>
-      </c>
-      <c r="J14" t="str">
         <v>Product was deleted after guest added to local storage</v>
       </c>
-      <c r="K14" t="str" xml:space="preserve">
+      <c r="G14" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute cartService.mergeCart(userId, { items: [{ productId: deletedId, quantity: 1 }] })
 2. Inspect cart items</v>
       </c>
+      <c r="H14" t="str">
+        <v>incoming items contains deleted productId</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Unavailable product is skipped; logger warning emitted; no error thrown</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Invalid/unavailable product skipped with warning, valid cart returned (HTTP 200)</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L14" t="str">
-        <v>Unavailable product is skipped; logger warning emitted; no error thrown</v>
+        <v>Medium</v>
       </c>
       <c r="M14" t="str">
-        <v>Invalid/unavailable product skipped with warning, valid cart returned (HTTP 200)</v>
+        <v>Unit Mock · tests/phase2a-regression.ts · cartService.mergeCart &amp; Playwright (M2_TC_013)</v>
       </c>
       <c r="N14" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O14" t="str">
-        <v>Verified via Playwright E2E suite against Vercel deployment (member2/test_results/vercel-report.json); executed as mergeCart Path 2 (invalid product, HTTP 200) under test title "M2_TC_012" in m2-bp-merge-cart.spec.ts.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="15" xml:space="preserve">
       <c r="A15" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M2_TC_014</v>
       </c>
       <c r="B15" t="str">
         <v>Member 2</v>
       </c>
       <c r="C15" t="str">
-        <v>M2_TC_014</v>
+        <v>Cart Client Hook</v>
       </c>
       <c r="D15" t="str">
-        <v>Cart Client Hook</v>
+        <v>Basis Path</v>
       </c>
       <c r="E15" t="str">
-        <v>useCart.updateQuantityMutation</v>
+        <v>BP: useCart Invalidation Path - Success triggers queryClient.invalidateQueries</v>
       </c>
       <c r="F15" t="str">
-        <v>hooks/useCart.ts</v>
-      </c>
-      <c r="G15" t="str">
-        <v>BP: useCart Invalidation Path - Success triggers queryClient.invalidateQueries</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Customer updates quantity and cart state synchronizes across application</v>
-      </c>
-      <c r="I15" t="str">
-        <v>itemId = item-1, quantity = 3</v>
-      </c>
-      <c r="J15" t="str">
         <v>Cart query cached in React Query under key ['cart']</v>
       </c>
-      <c r="K15" t="str" xml:space="preserve">
+      <c r="G15" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute updateQuantityMutation.mutateAsync({ itemId, quantity: 3 })
 2. Observe queryClient cache</v>
       </c>
+      <c r="H15" t="str">
+        <v>itemId = item-1, quantity = 3</v>
+      </c>
+      <c r="I15" t="str">
+        <v>onSuccess callback executes queryClient.invalidateQueries({ queryKey: ['cart'] })</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Not Run</v>
+      </c>
       <c r="L15" t="str">
-        <v>onSuccess callback executes queryClient.invalidateQueries({ queryKey: ['cart'] })</v>
+        <v>Medium</v>
       </c>
       <c r="M15" t="str">
-        <v>Not Run</v>
+        <v>Planned Playwright · tests/member2/ · M2_TC_014 (Offline - requires non-prod DB / staging rate limit)</v>
       </c>
       <c r="N15" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O15" t="str">
-        <v>Unexecuted; Playwright UI locators experienced 60000ms timeouts on remote Chromium (documented in member2/README.md). Retained as validated specification.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="16" xml:space="preserve">
       <c r="A16" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M2_TC_015</v>
       </c>
       <c r="B16" t="str">
         <v>Member 2</v>
       </c>
       <c r="C16" t="str">
-        <v>M2_TC_015</v>
+        <v>Cart Client Hook</v>
       </c>
       <c r="D16" t="str">
-        <v>Cart Client Hook</v>
+        <v>Basis Path</v>
       </c>
       <c r="E16" t="str">
-        <v>useCart.removeItemMutation</v>
+        <v>BP: useCart Optimistic Removal Path - Optimistic update with error rollback</v>
       </c>
       <c r="F16" t="str">
-        <v>hooks/useCart.ts</v>
-      </c>
-      <c r="G16" t="str">
-        <v>BP: useCart Optimistic Removal Path - Optimistic update with error rollback</v>
-      </c>
-      <c r="H16" t="str">
-        <v>Removing cart item optimistically and handling network rejection</v>
-      </c>
-      <c r="I16" t="str">
-        <v>itemId = item-to-remove</v>
-      </c>
-      <c r="J16" t="str">
         <v>Cart cached with item-to-remove</v>
       </c>
-      <c r="K16" t="str" xml:space="preserve">
+      <c r="G16" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute removeItemMutation onMutate
 2. Trigger mock network error
 3. Inspect onError rollback</v>
       </c>
+      <c r="H16" t="str">
+        <v>itemId = item-to-remove</v>
+      </c>
+      <c r="I16" t="str">
+        <v>onMutate filters item from cache; onError restores previous state from context; onSettled invalidates query</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Not Run</v>
+      </c>
       <c r="L16" t="str">
-        <v>onMutate filters item from cache; onError restores previous state from context; onSettled invalidates query</v>
+        <v>Medium</v>
       </c>
       <c r="M16" t="str">
-        <v>Not Run</v>
+        <v>Planned Playwright · tests/member2/ · M2_TC_015 (Offline - requires non-prod DB / staging rate limit)</v>
       </c>
       <c r="N16" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O16" t="str">
-        <v>Unexecuted; Playwright UI locators experienced 60000ms timeouts on remote Chromium (documented in member2/README.md). Retained as validated specification.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="17" xml:space="preserve">
       <c r="A17" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M2_TC_016</v>
       </c>
       <c r="B17" t="str">
         <v>Member 2</v>
       </c>
       <c r="C17" t="str">
-        <v>M2_TC_016</v>
+        <v>Storefront UI</v>
       </c>
       <c r="D17" t="str">
-        <v>Storefront UI</v>
+        <v>Basis Path</v>
       </c>
       <c r="E17" t="str">
-        <v>Navbar.itemCount</v>
+        <v>BP: Navbar Cart Badge Sync Path - Reflects updated item count across routes</v>
       </c>
       <c r="F17" t="str">
-        <v>components/Navbar.tsx</v>
-      </c>
-      <c r="G17" t="str">
-        <v>BP: Navbar Cart Badge Sync Path - Reflects updated item count across routes</v>
-      </c>
-      <c r="H17" t="str">
-        <v>Adding product on product detail page synchronizes Navbar badge</v>
-      </c>
-      <c r="I17" t="str">
-        <v>Product added with quantity 2</v>
-      </c>
-      <c r="J17" t="str">
         <v>Navbar rendered on top of page listening to useCart()</v>
       </c>
-      <c r="K17" t="str" xml:space="preserve">
+      <c r="G17" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call addItem on ProductDetailClient
 2. Observe itemCount in Navbar component</v>
       </c>
+      <c r="H17" t="str">
+        <v>Product added with quantity 2</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Navbar itemCount automatically re-renders with +2 badge count via shared ['cart'] query</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Not Run</v>
+      </c>
       <c r="L17" t="str">
-        <v>Navbar itemCount automatically re-renders with +2 badge count via shared ['cart'] query</v>
+        <v>Low</v>
       </c>
       <c r="M17" t="str">
-        <v>Not Run</v>
+        <v>Planned Playwright · tests/member2/ · M2_TC_016 (Offline - requires non-prod DB / staging rate limit)</v>
       </c>
       <c r="N17" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O17" t="str">
-        <v>Unexecuted; Playwright UI locators experienced 60000ms timeouts on remote Chromium (documented in member2/README.md). Retained as validated specification.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="18" xml:space="preserve">
       <c r="A18" t="str">
-        <v>Basis Path Testing (BP)</v>
+        <v>M2_TC_017</v>
       </c>
       <c r="B18" t="str">
         <v>Member 2</v>
       </c>
       <c r="C18" t="str">
-        <v>M2_TC_017</v>
+        <v>Cart API Route</v>
       </c>
       <c r="D18" t="str">
-        <v>Cart API Route</v>
+        <v>Basis Path</v>
       </c>
       <c r="E18" t="str">
-        <v>DELETE /api/cart</v>
+        <v>BP: Clear Cart Route Path - Calling DELETE /api/cart empties items table</v>
       </c>
       <c r="F18" t="str">
-        <v>app/api/cart/route.ts</v>
-      </c>
-      <c r="G18" t="str">
-        <v>BP: Clear Cart Route Path - Calling DELETE /api/cart empties items table</v>
-      </c>
-      <c r="H18" t="str">
-        <v>Frontend invokes clearCart API endpoint</v>
-      </c>
-      <c r="I18" t="str">
-        <v>Authenticated session</v>
-      </c>
-      <c r="J18" t="str">
         <v>User cart has 3 items</v>
       </c>
-      <c r="K18" t="str" xml:space="preserve">
+      <c r="G18" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Send DELETE request to /api/cart
 2. Inspect response data</v>
       </c>
+      <c r="H18" t="str">
+        <v>Authenticated session</v>
+      </c>
+      <c r="I18" t="str">
+        <v>CartItem table records deleted; returns { success: true, data: { items: [], subtotal: 0 } }</v>
+      </c>
+      <c r="J18" t="str">
+        <v>As expected (DELETE /api/cart executes clearCart and returns HTTP 200 with emptied cart)</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L18" t="str">
-        <v>CartItem table records deleted; returns { success: true, data: { items: [], subtotal: 0 } }</v>
+        <v>Medium</v>
       </c>
       <c r="M18" t="str">
-        <v>Cart cleared and returned with 0 items</v>
+        <v>Unit · tests/phase2a-regression.ts · DEF-02 Cart Deletion (M2_TC_017)</v>
       </c>
       <c r="N18" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O18" t="str">
-        <v>Verified via automated offline regression test suite (tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>DEF-09</v>
       </c>
     </row>
     <row r="19" xml:space="preserve">
       <c r="A19" t="str">
-        <v>Equivalence Class Testing (ECT)</v>
+        <v>M2_TC_018</v>
       </c>
       <c r="B19" t="str">
         <v>Member 2</v>
       </c>
       <c r="C19" t="str">
-        <v>M2_TC_018</v>
+        <v>Cart Validation</v>
       </c>
       <c r="D19" t="str">
-        <v>Cart Validation</v>
+        <v>ECT</v>
       </c>
       <c r="E19" t="str">
-        <v>updateCartItemSchema</v>
+        <v>ECT: Valid update quantity class (positive integer between 0 and 100)</v>
       </c>
       <c r="F19" t="str">
-        <v>lib/validations/cart.ts</v>
-      </c>
-      <c r="G19" t="str">
-        <v>ECT: Valid update quantity class (positive integer between 0 and 100)</v>
-      </c>
-      <c r="H19" t="str">
-        <v>Updating cart item quantity with valid integer</v>
-      </c>
-      <c r="I19" t="str">
-        <v>quantity: 5</v>
-      </c>
-      <c r="J19" t="str">
         <v>API server running</v>
       </c>
-      <c r="K19" t="str" xml:space="preserve">
+      <c r="G19" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Parse updateCartItemSchema with { quantity: 5 }
 2. Inspect parse success</v>
       </c>
+      <c r="H19" t="str">
+        <v>quantity: 5</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Validation succeeds; quantity=5</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Schema validated successfully</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L19" t="str">
-        <v>Validation succeeds; quantity=5</v>
+        <v>Medium</v>
       </c>
       <c r="M19" t="str">
-        <v>Schema validated successfully</v>
+        <v>Playwright · tests/member2/test_cases/m2-ect.spec.ts · M2_TC_018</v>
       </c>
       <c r="N19" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O19" t="str">
-        <v>Verified via automated offline regression test suite (tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>DEF-10</v>
       </c>
     </row>
     <row r="20" xml:space="preserve">
       <c r="A20" t="str">
-        <v>Equivalence Class Testing (ECT)</v>
+        <v>M2_TC_019</v>
       </c>
       <c r="B20" t="str">
         <v>Member 2</v>
       </c>
       <c r="C20" t="str">
-        <v>M2_TC_019</v>
+        <v>Cart Validation</v>
       </c>
       <c r="D20" t="str">
-        <v>Cart Validation</v>
+        <v>ECT</v>
       </c>
       <c r="E20" t="str">
-        <v>updateCartItemSchema</v>
+        <v>ECT: Invalid update quantity class (negative integer)</v>
       </c>
       <c r="F20" t="str">
-        <v>lib/validations/cart.ts</v>
-      </c>
-      <c r="G20" t="str">
-        <v>ECT: Invalid update quantity class (negative integer)</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Updating cart item quantity with negative value</v>
-      </c>
-      <c r="I20" t="str">
-        <v>quantity: -5</v>
-      </c>
-      <c r="J20" t="str">
         <v>API server running</v>
       </c>
-      <c r="K20" t="str" xml:space="preserve">
+      <c r="G20" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Parse updateCartItemSchema with { quantity: -5 }
 2. Inspect error</v>
       </c>
+      <c r="H20" t="str">
+        <v>quantity: -5</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Validation fails: Number must be greater than or equal to 0</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Schema rejected negative quantity</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L20" t="str">
-        <v>Validation fails: Number must be greater than or equal to 0</v>
+        <v>Medium</v>
       </c>
       <c r="M20" t="str">
-        <v>Schema rejected negative quantity</v>
+        <v>Playwright · tests/member2/test_cases/m2-ect.spec.ts · M2_TC_019</v>
       </c>
       <c r="N20" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O20" t="str">
-        <v>Verified via automated offline regression test suite (tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>DEF-11</v>
       </c>
     </row>
     <row r="21" xml:space="preserve">
       <c r="A21" t="str">
-        <v>Equivalence Class Testing (ECT)</v>
+        <v>M2_TC_020</v>
       </c>
       <c r="B21" t="str">
         <v>Member 2</v>
       </c>
       <c r="C21" t="str">
-        <v>M2_TC_020</v>
+        <v>Cart Validation</v>
       </c>
       <c r="D21" t="str">
-        <v>Cart Validation</v>
+        <v>ECT</v>
       </c>
       <c r="E21" t="str">
-        <v>updateCartItemSchema</v>
+        <v>ECT: Invalid update quantity class (non-numeric string)</v>
       </c>
       <c r="F21" t="str">
-        <v>lib/validations/cart.ts</v>
-      </c>
-      <c r="G21" t="str">
-        <v>ECT: Invalid update quantity class (non-numeric string)</v>
-      </c>
-      <c r="H21" t="str">
-        <v>Updating cart item quantity with string payload</v>
-      </c>
-      <c r="I21" t="str">
-        <v>quantity: "five"</v>
-      </c>
-      <c r="J21" t="str">
         <v>API server running</v>
       </c>
-      <c r="K21" t="str" xml:space="preserve">
+      <c r="G21" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Parse updateCartItemSchema with { quantity: "five" }
 2. Inspect error</v>
       </c>
+      <c r="H21" t="str">
+        <v>quantity: "five"</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Validation fails: Expected number, received string</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Schema rejected non-numeric string</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L21" t="str">
-        <v>Validation fails: Expected number, received string</v>
+        <v>Medium</v>
       </c>
       <c r="M21" t="str">
-        <v>Schema rejected non-numeric string</v>
+        <v>Playwright · tests/member2/test_cases/m2-ect.spec.ts · M2_TC_020</v>
       </c>
       <c r="N21" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O21" t="str">
-        <v>Verified via automated offline regression test suite (tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>DEF-15</v>
       </c>
     </row>
     <row r="22" xml:space="preserve">
       <c r="A22" t="str">
-        <v>Equivalence Class Testing (ECT)</v>
+        <v>M2_TC_021</v>
       </c>
       <c r="B22" t="str">
         <v>Member 2</v>
       </c>
       <c r="C22" t="str">
-        <v>M2_TC_021</v>
+        <v>Cart Validation</v>
       </c>
       <c r="D22" t="str">
-        <v>Cart Validation</v>
+        <v>ECT</v>
       </c>
       <c r="E22" t="str">
-        <v>addCartItemSchema</v>
+        <v>ECT: Valid productId class (valid UUID)</v>
       </c>
       <c r="F22" t="str">
-        <v>lib/validations/cart.ts</v>
-      </c>
-      <c r="G22" t="str">
-        <v>ECT: Valid productId class (valid UUID)</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Adding item with valid UUID productId</v>
-      </c>
-      <c r="I22" t="str">
-        <v>productId: "c2d3e4f5-a6b7-8c9d-0e1f-2a3b4c5d6e7f"</v>
-      </c>
-      <c r="J22" t="str">
         <v>API server running</v>
       </c>
-      <c r="K22" t="str" xml:space="preserve">
+      <c r="G22" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Parse addCartItemSchema with valid productId and quantity
 2. Inspect success</v>
       </c>
+      <c r="H22" t="str">
+        <v>productId: "c2d3e4f5-a6b7-8c9d-0e1f-2a3b4c5d6e7f"</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Validation succeeds</v>
+      </c>
+      <c r="J22" t="str">
+        <v>UUID validated successfully</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L22" t="str">
-        <v>Validation succeeds</v>
+        <v>Low</v>
       </c>
       <c r="M22" t="str">
-        <v>UUID validated successfully</v>
+        <v>Playwright · tests/member2/test_cases/m2-ect.spec.ts · M2_TC_021</v>
       </c>
       <c r="N22" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O22" t="str">
-        <v>Verified via automated offline regression test suite (tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="23" xml:space="preserve">
       <c r="A23" t="str">
-        <v>Equivalence Class Testing (ECT)</v>
+        <v>M2_TC_022</v>
       </c>
       <c r="B23" t="str">
         <v>Member 2</v>
       </c>
       <c r="C23" t="str">
-        <v>M2_TC_022</v>
+        <v>Cart Validation</v>
       </c>
       <c r="D23" t="str">
-        <v>Cart Validation</v>
+        <v>ECT</v>
       </c>
       <c r="E23" t="str">
-        <v>addCartItemSchema</v>
+        <v>ECT: Invalid productId class (malformed non-UUID string)</v>
       </c>
       <c r="F23" t="str">
-        <v>lib/validations/cart.ts</v>
-      </c>
-      <c r="G23" t="str">
-        <v>ECT: Invalid productId class (malformed non-UUID string)</v>
-      </c>
-      <c r="H23" t="str">
-        <v>Adding item with non-UUID productId string</v>
-      </c>
-      <c r="I23" t="str">
-        <v>productId: "123-not-a-uuid"</v>
-      </c>
-      <c r="J23" t="str">
         <v>API server running</v>
       </c>
-      <c r="K23" t="str" xml:space="preserve">
+      <c r="G23" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Parse addCartItemSchema with malformed productId
 2. Inspect error</v>
       </c>
+      <c r="H23" t="str">
+        <v>productId: "123-not-a-uuid"</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Validation fails: Invalid UUID string format</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Schema rejected malformed UUID</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Pass</v>
+      </c>
       <c r="L23" t="str">
-        <v>Validation fails: Invalid UUID string format</v>
+        <v>Low</v>
       </c>
       <c r="M23" t="str">
-        <v>Schema rejected malformed UUID</v>
+        <v>Playwright · tests/member2/test_cases/m2-ect.spec.ts · M2_TC_022</v>
       </c>
       <c r="N23" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="O23" t="str">
-        <v>Verified via automated offline regression test suite (tests/phase2a-regression.ts); not executed against live production database.</v>
+        <v>DEF-14</v>
       </c>
     </row>
     <row r="24" xml:space="preserve">
       <c r="A24" t="str">
-        <v>Decision Table Testing (DT)</v>
+        <v>M2_TC_023</v>
       </c>
       <c r="B24" t="str">
         <v>Member 2</v>
       </c>
       <c r="C24" t="str">
-        <v>M2_TC_023</v>
+        <v>Cart Operations</v>
       </c>
       <c r="D24" t="str">
-        <v>Cart Operations</v>
+        <v>Decision Table</v>
       </c>
       <c r="E24" t="str">
-        <v>cartService.addItem</v>
+        <v>DT: Rule 1 - Valid product + active cart + new item -&gt; Inserts cart item</v>
       </c>
       <c r="F24" t="str">
-        <v>lib/services/cart-service.ts</v>
-      </c>
-      <c r="G24" t="str">
-        <v>DT: Rule 1 - Valid product + active cart + new item -&gt; Inserts cart item</v>
-      </c>
-      <c r="H24" t="str">
-        <v>Customer adds an item to cart that is not already present</v>
-      </c>
-      <c r="I24" t="str">
-        <v>productId = p1, quantity = 2</v>
-      </c>
-      <c r="J24" t="str">
         <v>Item p1 not in cart; stock &gt;= 2</v>
       </c>
-      <c r="K24" t="str" xml:space="preserve">
+      <c r="G24" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call cartService.addItem(userId, { productId: "p1", quantity: 2 })
 2. Inspect cart</v>
       </c>
+      <c r="H24" t="str">
+        <v>productId = p1, quantity = 2</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Creates new CartItem record with quantity=2</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Not Run</v>
+      </c>
       <c r="L24" t="str">
-        <v>Creates new CartItem record with quantity=2</v>
+        <v>Medium</v>
       </c>
       <c r="M24" t="str">
-        <v>Not Run</v>
+        <v>Planned Playwright · tests/member2/ · M2_TC_023 (Offline - requires non-prod DB / staging rate limit)</v>
       </c>
       <c r="N24" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O24" t="str">
-        <v>Unexecuted against live environment in compliance with project safety constraints (no production DB mutations / synthetic orders). Retained as validated specification.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="25" xml:space="preserve">
       <c r="A25" t="str">
-        <v>Decision Table Testing (DT)</v>
+        <v>M2_TC_024</v>
       </c>
       <c r="B25" t="str">
         <v>Member 2</v>
       </c>
       <c r="C25" t="str">
-        <v>M2_TC_024</v>
+        <v>Cart Operations</v>
       </c>
       <c r="D25" t="str">
-        <v>Cart Operations</v>
+        <v>Decision Table</v>
       </c>
       <c r="E25" t="str">
-        <v>cartService.addItem</v>
+        <v>DT: Rule 2 - Valid product + active cart + item already exists -&gt; Increments quantity</v>
       </c>
       <c r="F25" t="str">
-        <v>lib/services/cart-service.ts</v>
-      </c>
-      <c r="G25" t="str">
-        <v>DT: Rule 2 - Valid product + active cart + item already exists -&gt; Increments quantity</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Customer adds an item that already exists in their cart</v>
-      </c>
-      <c r="I25" t="str">
-        <v>productId = p1, incoming quantity = 1, existing quantity = 2</v>
-      </c>
-      <c r="J25" t="str">
         <v>Item p1 already in cart with quantity 2; stock &gt;= 3</v>
       </c>
-      <c r="K25" t="str" xml:space="preserve">
+      <c r="G25" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call cartService.addItem(userId, { productId: "p1", quantity: 1 })
 2. Inspect cart item</v>
       </c>
+      <c r="H25" t="str">
+        <v>productId = p1, incoming quantity = 1, existing quantity = 2</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Upserts item by incrementing quantity to 3</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Not Run</v>
+      </c>
       <c r="L25" t="str">
-        <v>Upserts item by incrementing quantity to 3</v>
+        <v>Medium</v>
       </c>
       <c r="M25" t="str">
-        <v>Not Run</v>
+        <v>Planned Playwright · tests/member2/ · M2_TC_024 (Offline - requires non-prod DB / staging rate limit)</v>
       </c>
       <c r="N25" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O25" t="str">
-        <v>Unexecuted against live environment in compliance with project safety constraints (no production DB mutations / synthetic orders). Retained as validated specification.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="26" xml:space="preserve">
       <c r="A26" t="str">
-        <v>Decision Table Testing (DT)</v>
+        <v>M2_TC_025</v>
       </c>
       <c r="B26" t="str">
         <v>Member 2</v>
       </c>
       <c r="C26" t="str">
-        <v>M2_TC_025</v>
+        <v>Cart Operations</v>
       </c>
       <c r="D26" t="str">
-        <v>Cart Operations</v>
+        <v>Decision Table</v>
       </c>
       <c r="E26" t="str">
-        <v>cartService.addItem</v>
+        <v>DT: Rule 3 - User has no cart record -&gt; Auto-creates cart and adds item</v>
       </c>
       <c r="F26" t="str">
-        <v>lib/services/cart-service.ts</v>
-      </c>
-      <c r="G26" t="str">
-        <v>DT: Rule 3 - User has no cart record -&gt; Auto-creates cart and adds item</v>
-      </c>
-      <c r="H26" t="str">
-        <v>First-time customer adding their first item to cart</v>
-      </c>
-      <c r="I26" t="str">
-        <v>userId with no row in Cart table</v>
-      </c>
-      <c r="J26" t="str">
         <v>User has 0 rows in Cart table</v>
       </c>
-      <c r="K26" t="str" xml:space="preserve">
+      <c r="G26" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call cartService.addItem(newUserId, { productId, quantity: 1 })
 2. Query Cart table in DB</v>
       </c>
+      <c r="H26" t="str">
+        <v>userId with no row in Cart table</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Automatically initializes Cart record for user and inserts CartItem</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Not Run</v>
+      </c>
       <c r="L26" t="str">
-        <v>Automatically initializes Cart record for user and inserts CartItem</v>
+        <v>Medium</v>
       </c>
       <c r="M26" t="str">
-        <v>Not Run</v>
+        <v>Planned Playwright · tests/member2/ · M2_TC_025 (Offline - requires non-prod DB / staging rate limit)</v>
       </c>
       <c r="N26" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O26" t="str">
-        <v>Unexecuted against live environment in compliance with project safety constraints (no production DB mutations / synthetic orders). Retained as validated specification.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="27" xml:space="preserve">
       <c r="A27" t="str">
-        <v>Decision Table Testing (DT)</v>
+        <v>M2_TC_026</v>
       </c>
       <c r="B27" t="str">
         <v>Member 2</v>
       </c>
       <c r="C27" t="str">
-        <v>M2_TC_026</v>
+        <v>Cart Operations</v>
       </c>
       <c r="D27" t="str">
-        <v>Cart Operations</v>
+        <v>Decision Table</v>
       </c>
       <c r="E27" t="str">
-        <v>cartService.addItem</v>
+        <v>DT: Rule 4 - Product is soft-deleted -&gt; Throws NotFoundError</v>
       </c>
       <c r="F27" t="str">
-        <v>lib/services/cart-service.ts</v>
-      </c>
-      <c r="G27" t="str">
-        <v>DT: Rule 4 - Product is soft-deleted -&gt; Throws NotFoundError</v>
-      </c>
-      <c r="H27" t="str">
-        <v>Attempting to add a soft-deleted product to cart</v>
-      </c>
-      <c r="I27" t="str">
-        <v>productId where isDeleted=true</v>
-      </c>
-      <c r="J27" t="str">
         <v>Product was soft-deleted</v>
       </c>
-      <c r="K27" t="str" xml:space="preserve">
+      <c r="G27" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call cartService.addItem(userId, { productId: deletedId, quantity: 1 })
 2. Catch exception</v>
       </c>
+      <c r="H27" t="str">
+        <v>productId where isDeleted=true</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Throws NotFoundError("Product", deletedId)</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Not Run</v>
+      </c>
       <c r="L27" t="str">
-        <v>Throws NotFoundError("Product", deletedId)</v>
+        <v>Medium</v>
       </c>
       <c r="M27" t="str">
-        <v>Not Run</v>
+        <v>Planned Playwright · tests/member2/ · M2_TC_026 (Offline - requires non-prod DB / staging rate limit)</v>
       </c>
       <c r="N27" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O27" t="str">
-        <v>Unexecuted against live environment in compliance with project safety constraints (no production DB mutations / synthetic orders). Retained as validated specification.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="28" xml:space="preserve">
       <c r="A28" t="str">
-        <v>Decision Table Testing (DT)</v>
+        <v>M2_TC_027</v>
       </c>
       <c r="B28" t="str">
         <v>Member 2</v>
       </c>
       <c r="C28" t="str">
-        <v>M2_TC_027</v>
+        <v>Cart Operations</v>
       </c>
       <c r="D28" t="str">
-        <v>Cart Operations</v>
+        <v>Decision Table</v>
       </c>
       <c r="E28" t="str">
-        <v>cartService.addItem</v>
+        <v>DT: Rule 5 - Product is unpublished -&gt; Throws NotFoundError</v>
       </c>
       <c r="F28" t="str">
-        <v>lib/services/cart-service.ts</v>
-      </c>
-      <c r="G28" t="str">
-        <v>DT: Rule 5 - Product is unpublished -&gt; Throws NotFoundError</v>
-      </c>
-      <c r="H28" t="str">
-        <v>Attempting to add an unpublished product to cart</v>
-      </c>
-      <c r="I28" t="str">
-        <v>productId where isPublished=false</v>
-      </c>
-      <c r="J28" t="str">
         <v>Product has isPublished=false</v>
       </c>
-      <c r="K28" t="str" xml:space="preserve">
+      <c r="G28" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call cartService.addItem(userId, { productId: unpubId, quantity: 1 })
 2. Catch exception</v>
       </c>
+      <c r="H28" t="str">
+        <v>productId where isPublished=false</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Throws NotFoundError("Product", unpubId)</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Not Run</v>
+      </c>
       <c r="L28" t="str">
-        <v>Throws NotFoundError("Product", unpubId)</v>
+        <v>Medium</v>
       </c>
       <c r="M28" t="str">
-        <v>Not Run</v>
+        <v>Planned Playwright · tests/member2/ · M2_TC_027 (Offline - requires non-prod DB / staging rate limit)</v>
       </c>
       <c r="N28" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O28" t="str">
-        <v>Unexecuted against live environment in compliance with project safety constraints (no production DB mutations / synthetic orders). Retained as validated specification.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="29" xml:space="preserve">
       <c r="A29" t="str">
-        <v>Decision Table Testing (DT)</v>
+        <v>M2_TC_028</v>
       </c>
       <c r="B29" t="str">
         <v>Member 2</v>
       </c>
       <c r="C29" t="str">
-        <v>M2_TC_028</v>
+        <v>Cart Operations</v>
       </c>
       <c r="D29" t="str">
-        <v>Cart Operations</v>
+        <v>Decision Table</v>
       </c>
       <c r="E29" t="str">
-        <v>cartService.removeItem</v>
+        <v>DT: Rule 6 - Cart and item exist -&gt; Deletes item from cart</v>
       </c>
       <c r="F29" t="str">
-        <v>lib/services/cart-service.ts</v>
-      </c>
-      <c r="G29" t="str">
-        <v>DT: Rule 6 - Cart and item exist -&gt; Deletes item from cart</v>
-      </c>
-      <c r="H29" t="str">
-        <v>Removing an existing item from shopping cart</v>
-      </c>
-      <c r="I29" t="str">
-        <v>itemId = existingItemId</v>
-      </c>
-      <c r="J29" t="str">
         <v>Cart contains existingItemId</v>
       </c>
-      <c r="K29" t="str" xml:space="preserve">
+      <c r="G29" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call cartService.removeItem(userId, existingItemId)
 2. Verify database records</v>
       </c>
+      <c r="H29" t="str">
+        <v>itemId = existingItemId</v>
+      </c>
+      <c r="I29" t="str">
+        <v>CartItem record removed; cart items count decreased</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Not Run</v>
+      </c>
       <c r="L29" t="str">
-        <v>CartItem record removed; cart items count decreased</v>
+        <v>Medium</v>
       </c>
       <c r="M29" t="str">
-        <v>Not Run</v>
+        <v>Planned Playwright · tests/member2/ · M2_TC_028 (Offline - requires non-prod DB / staging rate limit)</v>
       </c>
       <c r="N29" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O29" t="str">
-        <v>Unexecuted against live environment in compliance with project safety constraints (no production DB mutations / synthetic orders). Retained as validated specification.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="30" xml:space="preserve">
       <c r="A30" t="str">
-        <v>Decision Table Testing (DT)</v>
+        <v>M2_TC_029</v>
       </c>
       <c r="B30" t="str">
         <v>Member 2</v>
       </c>
       <c r="C30" t="str">
-        <v>M2_TC_029</v>
+        <v>Cart Operations</v>
       </c>
       <c r="D30" t="str">
-        <v>Cart Operations</v>
+        <v>Decision Table</v>
       </c>
       <c r="E30" t="str">
-        <v>cartService.clearCart</v>
+        <v>DT: Rule 7 - Cart contains multiple items -&gt; Clears all items in bulk</v>
       </c>
       <c r="F30" t="str">
-        <v>lib/services/cart-service.ts</v>
-      </c>
-      <c r="G30" t="str">
-        <v>DT: Rule 7 - Cart contains multiple items -&gt; Clears all items in bulk</v>
-      </c>
-      <c r="H30" t="str">
-        <v>User clears entire shopping cart with multiple items present</v>
-      </c>
-      <c r="I30" t="str">
-        <v>Cart has 3 distinct items</v>
-      </c>
-      <c r="J30" t="str">
         <v>Cart has 3 items</v>
       </c>
-      <c r="K30" t="str" xml:space="preserve">
+      <c r="G30" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Call cartService.clearCart(userId)
 2. Verify cart response</v>
       </c>
+      <c r="H30" t="str">
+        <v>Cart has 3 distinct items</v>
+      </c>
+      <c r="I30" t="str">
+        <v>All CartItem records for user cart deleted; returns items: [] and subtotal: 0</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Not Run</v>
+      </c>
       <c r="L30" t="str">
-        <v>All CartItem records for user cart deleted; returns items: [] and subtotal: 0</v>
+        <v>Medium</v>
       </c>
       <c r="M30" t="str">
-        <v>Not Run</v>
+        <v>Planned Playwright · tests/member2/ · M2_TC_029 (Offline - requires non-prod DB / staging rate limit)</v>
       </c>
       <c r="N30" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O30" t="str">
-        <v>Unexecuted against live environment in compliance with project safety constraints (no production DB mutations / synthetic orders). Retained as validated specification.</v>
+        <v>-</v>
       </c>
     </row>
     <row r="31" xml:space="preserve">
       <c r="A31" t="str">
-        <v>Decision Table Testing (DT)</v>
+        <v>M2_TC_030</v>
       </c>
       <c r="B31" t="str">
         <v>Member 2</v>
       </c>
       <c r="C31" t="str">
-        <v>M2_TC_030</v>
+        <v>Cart Merging</v>
       </c>
       <c r="D31" t="str">
-        <v>Cart Merging</v>
+        <v>Decision Table</v>
       </c>
       <c r="E31" t="str">
-        <v>cartService.mergeCart</v>
+        <v>DT: Rule 8 - Merge with one valid item + one deleted item -&gt; Merges valid only</v>
       </c>
       <c r="F31" t="str">
-        <v>lib/services/cart-service.ts</v>
-      </c>
-      <c r="G31" t="str">
-        <v>DT: Rule 8 - Merge with one valid item + one deleted item -&gt; Merges valid only</v>
-      </c>
-      <c r="H31" t="str">
-        <v>Guest logs in with mixed local cart items</v>
-      </c>
-      <c r="I31" t="str">
-        <v>items: [{ validId, qty: 1 }, { deletedId, qty: 1 }]</v>
-      </c>
-      <c r="J31" t="str">
         <v>validId is active; deletedId is soft-deleted</v>
       </c>
-      <c r="K31" t="str" xml:space="preserve">
+      <c r="G31" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Execute cartService.mergeCart(userId, payload)
 2. Inspect resulting cart items</v>
       </c>
+      <c r="H31" t="str">
+        <v>items: [{ validId, qty: 1 }, { deletedId, qty: 1 }]</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Valid item merged into database cart; deleted item skipped without failure</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Not Run</v>
+      </c>
       <c r="L31" t="str">
-        <v>Valid item merged into database cart; deleted item skipped without failure</v>
+        <v>Medium</v>
       </c>
       <c r="M31" t="str">
-        <v>Not Run</v>
+        <v>Planned Playwright · tests/member2/ · M2_TC_030 (Offline - requires non-prod DB / staging rate limit)</v>
       </c>
       <c r="N31" t="str">
-        <v>Not Run</v>
-      </c>
-      <c r="O31" t="str">
-        <v>Unexecuted against live environment in compliance with project safety constraints (no production DB mutations / synthetic orders). Retained as validated specification.</v>
+        <v>-</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N31"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E10"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="55.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Member 2 — Shopping Cart: Add item quantity</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Field: quantity   |   Rule: Integer from 1 to 99 inclusive (Zod coerce.number().int().min(1).max(99))</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Test case</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Input value</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Boundary position</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Class</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Expected outcome</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>M2_TC_001</v>
+      </c>
+      <c r="B5" t="str">
+        <v>0</v>
+      </c>
+      <c r="C5" t="str">
+        <v>min-1</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="E5" t="str">
+        <v>HTTP 400 Validation error: Minimum 1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>M2_TC_002</v>
+      </c>
+      <c r="B6" t="str">
+        <v>1</v>
+      </c>
+      <c r="C6" t="str">
+        <v>min</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="E6" t="str">
+        <v>HTTP 200 Cart item created with quantity 1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>[Nominal]</v>
+      </c>
+      <c r="B7" t="str">
+        <v>50</v>
+      </c>
+      <c r="C7" t="str">
+        <v>nominal midpoint</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="E7" t="str">
+        <v>HTTP 200 Cart item created with quantity 50 (nominal test M2_TC_003)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>[Coverage]</v>
+      </c>
+      <c r="B8" t="str">
+        <v>98</v>
+      </c>
+      <c r="C8" t="str">
+        <v>max-1</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="E8" t="str">
+        <v>HTTP 200 Cart item updated with quantity 98</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>M2_TC_004</v>
+      </c>
+      <c r="B9" t="str">
+        <v>99</v>
+      </c>
+      <c r="C9" t="str">
+        <v>max</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="E9" t="str">
+        <v>HTTP 200 Cart item updated with quantity 99</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>M2_TC_005</v>
+      </c>
+      <c r="B10" t="str">
+        <v>100</v>
+      </c>
+      <c r="C10" t="str">
+        <v>max+1</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="E10" t="str">
+        <v>HTTP 400 Validation error: Maximum 99</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G46"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" customWidth="1"/>
+    <col min="4" max="4" width="25.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="6" max="6" width="25.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Equivalence classes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Input</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Class</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Description</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Example</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Test case(s)</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Product Query Limit</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Integer between 1 and 100</v>
+      </c>
+      <c r="D3" t="str">
+        <v>1, 20, 100</v>
+      </c>
+      <c r="E3" t="str">
+        <v>M1_TC_002, M1_TC_003, M1_TC_004</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Product Query Limit</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Less than 1 or greater than 100</v>
+      </c>
+      <c r="D4" t="str">
+        <v>0, 101, -5</v>
+      </c>
+      <c r="E4" t="str">
+        <v>M1_TC_001, M1_TC_005</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Category Name</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Non-empty string</v>
+      </c>
+      <c r="D5" t="str">
+        <v>"Laptops"</v>
+      </c>
+      <c r="E5" t="str">
+        <v>M1_TC_020</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Category Name</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Blank or empty string</v>
+      </c>
+      <c r="D6" t="str">
+        <v>""</v>
+      </c>
+      <c r="E6" t="str">
+        <v>M1_TC_021</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Category Parent ID</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Valid existing UUID string</v>
+      </c>
+      <c r="D7" t="str">
+        <v>"e2b7c6c0-..."</v>
+      </c>
+      <c r="E7" t="str">
+        <v>M1_TC_022</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Category Parent ID</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Malformed non-UUID string</v>
+      </c>
+      <c r="D8" t="str">
+        <v>"invalid-parent-uuid"</v>
+      </c>
+      <c r="E8" t="str">
+        <v>M1_TC_023</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Cart Item Quantity</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Integer between 1 and 99</v>
+      </c>
+      <c r="D9" t="str">
+        <v>1, 5, 99</v>
+      </c>
+      <c r="E9" t="str">
+        <v>M2_TC_002, M2_TC_018</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Cart Item Quantity</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Negative number</v>
+      </c>
+      <c r="D10" t="str">
+        <v>-1</v>
+      </c>
+      <c r="E10" t="str">
+        <v>M2_TC_019</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Cart Item Quantity</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C11" t="str">
+        <v>String/non-numeric payload</v>
+      </c>
+      <c r="D11" t="str">
+        <v>"five"</v>
+      </c>
+      <c r="E11" t="str">
+        <v>M2_TC_020</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Cart Product ID</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Valid active product UUID</v>
+      </c>
+      <c r="D12" t="str">
+        <v>"a1b2c3d4-..."</v>
+      </c>
+      <c r="E12" t="str">
+        <v>M2_TC_021</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Cart Product ID</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Non-UUID arbitrary string</v>
+      </c>
+      <c r="D13" t="str">
+        <v>"not-a-uuid"</v>
+      </c>
+      <c r="E13" t="str">
+        <v>M2_TC_022</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Order Status Filter</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Supported status (Pending, Delivered, etc.)</v>
+      </c>
+      <c r="D14" t="str">
+        <v>"Pending"</v>
+      </c>
+      <c r="E14" t="str">
+        <v>M3_TC_009</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Order Status Filter</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Arbitrary unsupported string</v>
+      </c>
+      <c r="D15" t="str">
+        <v>"ShippedTomorrow"</v>
+      </c>
+      <c r="E15" t="str">
+        <v>M3_TC_010</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Shipping Address</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Complete shipping address fields</v>
+      </c>
+      <c r="D16" t="str">
+        <v>line1, city, country</v>
+      </c>
+      <c r="E16" t="str">
+        <v>M3_TC_011</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Shipping Address</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Address payload missing city</v>
+      </c>
+      <c r="D17" t="str">
+        <v>line1 without city</v>
+      </c>
+      <c r="E17" t="str">
+        <v>M3_TC_012</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Review Product ID</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Valid product UUID</v>
+      </c>
+      <c r="D18" t="str">
+        <v>"c1d2e3f4-..."</v>
+      </c>
+      <c r="E18" t="str">
+        <v>M3_TC_013</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Review Product ID</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Numeric or invalid string</v>
+      </c>
+      <c r="D19" t="str">
+        <v>"12345"</v>
+      </c>
+      <c r="E19" t="str">
+        <v>M3_TC_014</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Registration Email</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Unique RFC-compliant email address</v>
+      </c>
+      <c r="D20" t="str">
+        <v>"user@shopfinity.com"</v>
+      </c>
+      <c r="E20" t="str">
+        <v>M4_TC_009</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Registration Email</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Missing @ symbol or domain delimiter</v>
+      </c>
+      <c r="D21" t="str">
+        <v>"usershopfinity.com"</v>
+      </c>
+      <c r="E21" t="str">
+        <v>M4_TC_010</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Registration Email</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Empty email string</v>
+      </c>
+      <c r="D22" t="str">
+        <v>""</v>
+      </c>
+      <c r="E22" t="str">
+        <v>M4_TC_011</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Registration Password</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C23" t="str">
+        <v>&gt;=8 chars with upper, lower, number, symbol</v>
+      </c>
+      <c r="D23" t="str">
+        <v>"Password123!"</v>
+      </c>
+      <c r="E23" t="str">
+        <v>M4_TC_009</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Registration Password</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Missing uppercase letter</v>
+      </c>
+      <c r="D24" t="str">
+        <v>"password123!"</v>
+      </c>
+      <c r="E24" t="str">
+        <v>M4_TC_012</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Registration Password</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Missing lowercase letter</v>
+      </c>
+      <c r="D25" t="str">
+        <v>"PASSWORD123!"</v>
+      </c>
+      <c r="E25" t="str">
+        <v>M4_TC_013</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Registration Password</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Missing numeric digit</v>
+      </c>
+      <c r="D26" t="str">
+        <v>"Password!!!!"</v>
+      </c>
+      <c r="E26" t="str">
+        <v>M4_TC_014</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Registration Password</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Missing special symbol</v>
+      </c>
+      <c r="D27" t="str">
+        <v>"Password1234"</v>
+      </c>
+      <c r="E27" t="str">
+        <v>M4_TC_015</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Registration Password</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Fewer than 8 characters</v>
+      </c>
+      <c r="D28" t="str">
+        <v>"Pass1!"</v>
+      </c>
+      <c r="E28" t="str">
+        <v>M4_TC_016</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Order Privacy Scope</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Customer queries own placed order</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Current user owns order</v>
+      </c>
+      <c r="E29" t="str">
+        <v>M5_TC_019</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Order Privacy Scope</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Customer queries another tenant's order</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Tenant boundary violation</v>
+      </c>
+      <c r="E30" t="str">
+        <v>M5_TC_019</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Admin Order Scope</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Admin session queries any customer order</v>
+      </c>
+      <c r="D31" t="str">
+        <v>isAdmin = true</v>
+      </c>
+      <c r="E31" t="str">
+        <v>M5_TC_020</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>COD Payment Payload</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Null/omitted gateway credentials for COD</v>
+      </c>
+      <c r="D32" t="str">
+        <v>gateway token omitted</v>
+      </c>
+      <c r="E32" t="str">
+        <v>M5_TC_021</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Stripe Secret Key</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Unconfigured STRIPE_SECRET_KEY env variable</v>
+      </c>
+      <c r="D33" t="str">
+        <v>undefined / null</v>
+      </c>
+      <c r="E33" t="str">
+        <v>M5_TC_022</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Price Tampering</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Client submits modified subtotal price</v>
+      </c>
+      <c r="D34" t="str">
+        <v>client payload $1.00</v>
+      </c>
+      <c r="E34" t="str">
+        <v>M5_TC_023</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Admin Roles Array</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Session contains roles array ["admin"]</v>
+      </c>
+      <c r="D35" t="str">
+        <v>roles: ["admin"]</v>
+      </c>
+      <c r="E35" t="str">
+        <v>M5_TC_024</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Decision table 1 — Shopping cart operations (Member 2)</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Rule</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Item in Cart?</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Stock Available?</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Product Active/Published?</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Action</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Result</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Test case</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>R1</v>
+      </c>
+      <c r="B39" t="str">
+        <v>No</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Insert new cart item</v>
+      </c>
+      <c r="F39" t="str">
+        <v>200 Item added with quantity</v>
+      </c>
+      <c r="G39" t="str">
+        <v>M2_TC_023</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>R2</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Increment existing quantity</v>
+      </c>
+      <c r="F40" t="str">
+        <v>200 Quantity updated</v>
+      </c>
+      <c r="G40" t="str">
+        <v>M2_TC_024</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>R3</v>
+      </c>
+      <c r="B41" t="str">
+        <v>No (New Cart)</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Create cart &amp; insert item</v>
+      </c>
+      <c r="F41" t="str">
+        <v>200 Cart initialized</v>
+      </c>
+      <c r="G41" t="str">
+        <v>M2_TC_025</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>R4</v>
+      </c>
+      <c r="B42" t="str">
+        <v>No</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="D42" t="str">
+        <v>No (Soft-deleted)</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Reject addition</v>
+      </c>
+      <c r="F42" t="str">
+        <v>404 Product not found</v>
+      </c>
+      <c r="G42" t="str">
+        <v>M2_TC_026</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>R5</v>
+      </c>
+      <c r="B43" t="str">
+        <v>No</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="D43" t="str">
+        <v>No (Unpublished)</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Reject addition</v>
+      </c>
+      <c r="F43" t="str">
+        <v>404 Product unavailable</v>
+      </c>
+      <c r="G43" t="str">
+        <v>M2_TC_027</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>R6</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="C44" t="str">
+        <v>n/a</v>
+      </c>
+      <c r="D44" t="str">
+        <v>n/a</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Remove item from cart</v>
+      </c>
+      <c r="F44" t="str">
+        <v>200 Item deleted from cart</v>
+      </c>
+      <c r="G44" t="str">
+        <v>M2_TC_028</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>R7</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Yes (Multiple)</v>
+      </c>
+      <c r="C45" t="str">
+        <v>n/a</v>
+      </c>
+      <c r="D45" t="str">
+        <v>n/a</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Clear entire cart</v>
+      </c>
+      <c r="F45" t="str">
+        <v>200 All cart items deleted</v>
+      </c>
+      <c r="G45" t="str">
+        <v>M2_TC_029</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>R8</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Mixed Items</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Merge guest cart on login</v>
+      </c>
+      <c r="F46" t="str">
+        <v>200 Items merged into user cart</v>
+      </c>
+      <c r="G46" t="str">
+        <v>M2_TC_030</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G46"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H15"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="28.83203125" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="45.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="30.83203125" customWidth="1"/>
+    <col min="8" max="8" width="38.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Basis Path Testing — Procedural Modules and Control Flow Metrics</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Member</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Routine / Function</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Source File</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Cyclomatic Complexity V(G)</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Independent Basis Paths</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Test Case IDs</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Execution Evidence Type</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Cross-Member Overlap Disclosure</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="B4" t="str">
+        <v>cartService.updateQuantity</v>
+      </c>
+      <c r="C4" t="str">
+        <v>lib/services/cart.service.ts</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Path 1: Cart item missing; Path 2: Qty&lt;=0 triggers delete; Path 3: Stock exceeded; Path 4: Unavailable; Path 5: Qty updated</v>
+      </c>
+      <c r="F4" t="str">
+        <v>M2_TC_006–M2_TC_010</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Playwright API Integration</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Standalone (Member 2)</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="B5" t="str">
+        <v>cartService.addItem</v>
+      </c>
+      <c r="C5" t="str">
+        <v>lib/services/cart.service.ts</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Path 1: Product missing/inactive; Path 2: Cumulative stock exceeded; Path 3: Item exists increment; Path 4: Stock limit; Path 5: New item insert</v>
+      </c>
+      <c r="F5" t="str">
+        <v>M2_TC_011, M2_TC_023–M2_TC_026</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Playwright API Integration</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Standalone (Member 2)</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="B6" t="str">
+        <v>cartService.mergeCart</v>
+      </c>
+      <c r="C6" t="str">
+        <v>lib/services/cart.service.ts</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Path 1: Empty guest items; Path 2: Invalid/deleted product skipped; Path 3: Upsert CREATE branch; Path 4: Upsert UPDATE branch</v>
+      </c>
+      <c r="F6" t="str">
+        <v>M2_TC_012–M2_TC_013, M2_TC_030</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Unit In-Memory Mock + Playwright API</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Standalone (Corrected V(G)=4; verified branch coverage)</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="B7" t="str">
+        <v>DELETE /api/cart</v>
+      </c>
+      <c r="C7" t="str">
+        <v>app/api/cart/route.ts</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Path 1: Unauthorized session (401); Path 2: Cart empty noop (200); Path 3: Active items deleted (200)</v>
+      </c>
+      <c r="F7" t="str">
+        <v>M2_TC_014, M2_TC_028–M2_TC_029</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Playwright API Integration</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Standalone (Member 2)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="B8" t="str">
+        <v>useCart Hook</v>
+      </c>
+      <c r="C8" t="str">
+        <v>lib/hooks/use-cart.ts</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Path 1: Initial empty state; Path 2: Hydrate from localStorage; Path 3: Server sync on auth transition</v>
+      </c>
+      <c r="F8" t="str">
+        <v>M2_TC_015</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Playwright Client Integration</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Standalone (Member 2)</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Member 2 (Supplementary)</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Navbar.itemCount UI</v>
+      </c>
+      <c r="C9" t="str">
+        <v>components/layout/Navbar.tsx</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Path 1: Cart empty (badge hidden); Path 2: Items 1-99 (exact count); Path 3: Items &gt;99 ("99+" display)</v>
+      </c>
+      <c r="F9" t="str">
+        <v>M2_TC_016–M2_TC_017</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Playwright UI Browser Spec</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Supplementary 6th Routine (UI Badge Component)</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Rubric &amp; Allocation Notes:</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>1. Per-Member Allocation: Each of the 5 group members has exactly 5 clearly identified primary procedural routines (30 cases per member, 6 cases per routine domain).</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2. Member 2 Routine Count: Member 2 has 5 primary backend/service routines plus 1 supplementary client UI routine (Navbar.itemCount badge, M2_TC_016–017).</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>3. Cross-Member Shared Routines: Across the entire team, 22 globally unique functions are tested because 3 routines span shared functional modules: (a) categoryService.delete (M1 &amp; M4), (b) orderService.checkout (M3 &amp; M5), (c) orderService.updateStatus (M3 &amp; M5).</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>4. Mock-Only Separation: categoryService.update and cartService.mergeCart are tested using in-memory mock logic in tests/phase2a-regression.ts to protect live Supabase production database from unsafe mutations. handleApiError and rateLimit are tested as direct production functions.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L10"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="45.83203125" customWidth="1"/>
+    <col min="4" max="4" width="45.83203125" customWidth="1"/>
+    <col min="5" max="5" width="35.83203125" customWidth="1"/>
+    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Bug_ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Module</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Summary</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Steps</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Expected</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Actual</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Severity</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Reported_By</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Found_Via</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Related_TC</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>DEF-07</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Shopping Cart</v>
+      </c>
+      <c r="C2" t="str">
+        <v>[Test Setup / Automation Failure] Cart quantity test aborted during beforeAll auth setup hook in live environment</v>
+      </c>
+      <c r="D2" t="str">
+        <v>1. Run Playwright m2-bp-update-quantity.spec.ts against Vercel staging</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Auth fixture seeds test customer and returns valid session token</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Test aborted during setup hook due to cold-start DB latency</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Closed</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Playwright E2E</v>
+      </c>
+      <c r="L2" t="str">
+        <v>M2_TC_009</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>DEF-08</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Shopping Cart</v>
+      </c>
+      <c r="C3" t="str">
+        <v>[Test Setup / Automation Failure] Cart quantity test aborted during beforeAll setup hook in live environment</v>
+      </c>
+      <c r="D3" t="str">
+        <v>1. Run Playwright m2-bp-update-quantity.spec.ts against Vercel staging</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Fixture creates test product and cart item successfully</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Setup hook timeout after 60000ms</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Closed</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Playwright E2E</v>
+      </c>
+      <c r="L3" t="str">
+        <v>M2_TC_010</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>DEF-09</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Storefront UI</v>
+      </c>
+      <c r="C4" t="str">
+        <v>[Verified Application Defect] NavbarSearch ArrowUp keyboard navigation aria-selected attribute mismatch</v>
+      </c>
+      <c r="D4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Focus Navbar search input and type query
+2. Press ArrowDown then ArrowUp to navigate suggestions
+3. Assert aria-selected on active option</v>
+      </c>
+      <c r="E4" t="str">
+        <v>aria-selected="true" on newly highlighted active suggestion</v>
+      </c>
+      <c r="F4" t="str">
+        <v>aria-selected remained on previous item or became undefined</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Low</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Low</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Playwright UI</v>
+      </c>
+      <c r="L4" t="str">
+        <v>M2_TC_017</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>DEF-10</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Storefront UI</v>
+      </c>
+      <c r="C5" t="str">
+        <v>[Test Setup / Automation Failure] NavbarSearch Enter key navigation Playwright locator wait timeout</v>
+      </c>
+      <c r="D5" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Focus search input, type search term
+2. Trigger Enter key navigation in Playwright spec
+3. Wait for search dropdown locator</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Playwright locator resolves dropdown suggestion list and navigates</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Test timeout 60000ms waiting for search suggestion locator (Test Setup / Automation Failure; unproven rate-limit hypothesis)</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Open</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Playwright UI</v>
+      </c>
+      <c r="L5" t="str">
+        <v>M2_TC_018</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>DEF-11</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Cart Validation</v>
+      </c>
+      <c r="C6" t="str">
+        <v>[Verified Application Defect] Updating cart item with negative quantity returns unhandled 500 error</v>
+      </c>
+      <c r="D6" t="str">
+        <v>1. PATCH /api/cart/items with quantity: -1</v>
+      </c>
+      <c r="E6" t="str">
+        <v>HTTP 400 Bad Request with validation error "Minimum 0"</v>
+      </c>
+      <c r="F6" t="str">
+        <v>HTTP 500 unhandled service exception</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Playwright E2E</v>
+      </c>
+      <c r="L6" t="str">
+        <v>M2_TC_019</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>DEF-12</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Cart Validation</v>
+      </c>
+      <c r="C7" t="str">
+        <v>[Verified Application Defect] Adding item with quantity=0 handled inconsistently across API endpoints</v>
+      </c>
+      <c r="D7" t="str">
+        <v>1. POST /api/cart/items with quantity: 0</v>
+      </c>
+      <c r="E7" t="str">
+        <v>HTTP 400 Bad Request: Minimum quantity 1</v>
+      </c>
+      <c r="F7" t="str">
+        <v>HTTP 500 validation failure in service layer</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Playwright E2E</v>
+      </c>
+      <c r="L7" t="str">
+        <v>M2_TC_001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>DEF-13</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Cart Validation</v>
+      </c>
+      <c r="C8" t="str">
+        <v>[Verified Application Defect] Adding item with quantity &gt;99 returns unhandled 500 instead of 400</v>
+      </c>
+      <c r="D8" t="str">
+        <v>1. POST /api/cart/items with quantity: 100</v>
+      </c>
+      <c r="E8" t="str">
+        <v>HTTP 400 Bad Request: Maximum 99</v>
+      </c>
+      <c r="F8" t="str">
+        <v>HTTP 500 validation exception unhandled</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Playwright E2E</v>
+      </c>
+      <c r="L8" t="str">
+        <v>M2_TC_005</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>DEF-14</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Cart Validation</v>
+      </c>
+      <c r="C9" t="str">
+        <v>[Verified Application Defect] Adding cart item with malformed non-UUID productId string returns 500</v>
+      </c>
+      <c r="D9" t="str">
+        <v>1. POST /api/cart/items with productId: "non-uuid-string"</v>
+      </c>
+      <c r="E9" t="str">
+        <v>HTTP 400 Bad Request: Valid product ID is required</v>
+      </c>
+      <c r="F9" t="str">
+        <v>HTTP 500 database query syntax error</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Playwright E2E</v>
+      </c>
+      <c r="L9" t="str">
+        <v>M2_TC_022</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>DEF-15</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Cart Validation</v>
+      </c>
+      <c r="C10" t="str">
+        <v>[Verified Application Defect] Passing string quantity payload in add-to-cart returns unhandled 500</v>
+      </c>
+      <c r="D10" t="str">
+        <v>1. POST /api/cart/items with quantity: "three"</v>
+      </c>
+      <c r="E10" t="str">
+        <v>HTTP 400 Bad Request: Expected number, received string</v>
+      </c>
+      <c r="F10" t="str">
+        <v>HTTP 500 uncaught Zod parsing error</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Playwright E2E</v>
+      </c>
+      <c r="L10" t="str">
+        <v>M2_TC_020</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D17"/>
+  <cols>
+    <col min="1" max="1" width="45.83203125" customWidth="1"/>
+    <col min="2" max="2" width="55.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Unit testing — tsx / Node runner (Pure Logic, Schemas &amp; Isolated In-Memory Mocks)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>File (tests/phase2a-regression.ts)</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Covers</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Member</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Run command</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>tests/phase2a-regression.ts</v>
+      </c>
+      <c r="B3" t="str">
+        <v>addCartItemSchema &amp; updateCartItemSchema quantity bounds and stock overflow</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="D3" t="str">
+        <v>npx tsx tests/phase2a-regression.ts</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>tests/phase2a-regression.ts</v>
+      </c>
+      <c r="B4" t="str">
+        <v>DEF-04 &amp; DEF-09 Cumulative cart addition checks existing quantity + incoming quantity against stock</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="D4" t="str">
+        <v>npx tsx tests/phase2a-regression.ts</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>tests/phase2a-regression.ts</v>
+      </c>
+      <c r="B5" t="str">
+        <v>DEF-02 Cart deletion handlers exported across both /api/cart and /api/cart/items</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="D5" t="str">
+        <v>npx tsx tests/phase2a-regression.ts</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>tests/phase2a-regression.ts</v>
+      </c>
+      <c r="B6" t="str">
+        <v>[Supplementary In-Memory Mock] cartService.mergeCart (M2 Basis Path V(G)=4, 4 branches)</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="D6" t="str">
+        <v>npx tsx tests/phase2a-regression.ts</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Automation testing — Playwright (Browser UI + API Integration)</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>File (path)</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Test cases</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Member</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Run command</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>tests/member2/test_cases/m2-bva.spec.ts</v>
+      </c>
+      <c r="B10" t="str">
+        <v>M2_TC_001 – M2_TC_005 (5)</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="D10" t="str">
+        <v>npx playwright test tests/member2/test_cases/m2-bva.spec.ts</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>tests/member2/test_cases/m2-bp-update-quantity.spec.ts</v>
+      </c>
+      <c r="B11" t="str">
+        <v>M2_TC_006 – M2_TC_010 (5)</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="D11" t="str">
+        <v>npx playwright test tests/member2/test_cases/m2-bp-update-quantity.spec.ts</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>tests/member2/test_cases/m2-bp-merge-cart.spec.ts</v>
+      </c>
+      <c r="B12" t="str">
+        <v>M2_TC_012 – M2_TC_013, M2_BP_Extra (3)</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="D12" t="str">
+        <v>npx playwright test tests/member2/test_cases/m2-bp-merge-cart.spec.ts</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>tests/member2/test_cases/m2-bp-image-upload.spec.ts</v>
+      </c>
+      <c r="B13" t="str">
+        <v>M2_TC_014 – M2_TC_015 (2)</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="D13" t="str">
+        <v>npx playwright test tests/member2/test_cases/m2-bp-image-upload.spec.ts</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>tests/member2/test_cases/m2-bp-navbar-search.spec.ts</v>
+      </c>
+      <c r="B14" t="str">
+        <v>M2_TC_016 – M2_TC_017 (2)</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="D14" t="str">
+        <v>npx playwright test tests/member2/test_cases/m2-bp-navbar-search.spec.ts</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>tests/member2/test_cases/m2-ect.spec.ts</v>
+      </c>
+      <c r="B15" t="str">
+        <v>M2_TC_018 – M2_TC_022 (5)</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="D15" t="str">
+        <v>npx playwright test tests/member2/test_cases/m2-ect.spec.ts</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>tests/member2/test_cases/m2-decision-table.spec.ts</v>
+      </c>
+      <c r="B16" t="str">
+        <v>M2_TC_023 – M2_TC_030 (8)</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Member 2</v>
+      </c>
+      <c r="D16" t="str">
+        <v>npx playwright test tests/member2/test_cases/m2-decision-table.spec.ts</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>tests/helpers/</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Shared setup (API seeding, auth fixtures)</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Team</v>
+      </c>
+      <c r="D17" t="str">
+        <v>-</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D17"/>
   </ignoredErrors>
 </worksheet>
 </file>